--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO 2000.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO 2000.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347437</t>
+          <t>282275</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89602</t>
+          <t>79776</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LUIS ANGEL</t>
+          <t>CRISTINA JOSELIN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>ALDRETE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>CAMARILLO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,47 +740,43 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6645735619</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>COND AZALOEA</t>
-        </is>
-      </c>
+          <t>6645027425</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>02-10-1995</t>
+          <t>07-02-2009</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>OCTUBRE95TG@GMAIL.COM</t>
+          <t>CRISJAC@YAHOO.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>02-03-2026 08:13:46</t>
+          <t>08-03-2025 09:37:53</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -790,29 +786,21 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 08:17:15</t>
+          <t>03-03-2026 15:22:07</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>02-03-2026 08:16:13</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -820,7 +808,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26120522783750008947</t>
+          <t>26120522843690009284</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -832,24 +820,24 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Aram Geronimo Garay Alvarado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347464</t>
+          <t>347405</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89629</t>
+          <t>89570</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +847,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>THELMA NOEMI</t>
+          <t>ITZEL KARINA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SALDIVAR</t>
+          <t>GAXIOLA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,12 +867,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3441658484</t>
+          <t>6647511082</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PRIV</t>
+          <t>BOCA DELOBO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -894,17 +882,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>15-12-1994</t>
+          <t>04-01-2005</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SALDIVARNOEMI07@GMAIL.COM</t>
+          <t>KGAXIOLA51@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 09:26:02</t>
+          <t>02-03-2026 06:37:04</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -914,22 +902,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 09:27:31</t>
+          <t>02-03-2026 06:39:25</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -939,7 +927,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 09:27:12</t>
+          <t>02-03-2026 06:38:46</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -959,36 +947,36 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26120522785900008969</t>
+          <t>26120522780920008926</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Uriel  Aguilar Dionisio</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347405</t>
+          <t>347441</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89570</t>
+          <t>89606</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +986,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ITZEL KARINA</t>
+          <t>RAUL DUARDO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GAXIOLA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>OSORNIO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,32 +1006,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6647511082</t>
+          <t>6648202291</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BOCA DELOBO</t>
+          <t>C HDA SAN MIGUEL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>04-01-2005</t>
+          <t>15-11-2003</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>KGAXIOLA51@GMAIL.COM</t>
+          <t>TORRESRAUL383@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 06:37:04</t>
+          <t>02-03-2026 08:26:25</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1068,7 +1056,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 06:39:25</t>
+          <t>02-03-2026 08:29:25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1078,7 +1066,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 06:38:46</t>
+          <t>02-03-2026 08:29:09</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1098,7 +1086,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26120522780920008926</t>
+          <t>26120522784170008951</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1110,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Kevin Uriel  Aguilar Dionisio</t>
+          <t>Aram Geronimo Garay Alvarado</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1122,12 +1110,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347441</t>
+          <t>265886</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89606</t>
+          <t>63390</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1125,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RAUL DUARDO</t>
+          <t xml:space="preserve">MARTIZA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>BLANCARTE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OSORNIO</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,32 +1145,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6648202291</t>
+          <t>6645955683</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C HDA SAN MIGUEL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>15-11-2003</t>
+          <t>08-06-1997</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>TORRESRAUL383@GMAIL.COM</t>
+          <t>08.MARITZAB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 08:26:25</t>
+          <t>12-11-2024 13:28:20</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1192,32 +1180,32 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 08:29:25</t>
+          <t>03-03-2026 20:34:26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 08:29:09</t>
+          <t>03-03-2026 20:31:06</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1237,36 +1225,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26120522784170008951</t>
+          <t>26120522861150009379</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Aram Geronimo Garay Alvarado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347444</t>
+          <t>347913</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89609</t>
+          <t>90078</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1264,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VIVIAN ARLETH</t>
+          <t>JESUS ALONSO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RENTERIA</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,32 +1284,28 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6633288198</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>COL CERRO COL</t>
-        </is>
-      </c>
+          <t>6642581633</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>07-10-2005</t>
+          <t>02-01-1991</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>LILIANVALLES171@GMAIL.COM</t>
+          <t>JESUSLONSOASN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 08:32:44</t>
+          <t>02-03-2026 21:34:11</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1331,22 +1315,22 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 08:35:45</t>
+          <t>02-03-2026 21:37:54</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1354,21 +1338,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>02-03-2026 08:34:41</t>
-        </is>
-      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1376,36 +1352,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26120522784290008953</t>
+          <t>26120522820940009167</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Aram Geronimo Garay Alvarado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347913</t>
+          <t>347942</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90078</t>
+          <t>90107</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1391,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>JESUS ALONSO</t>
+          <t>BETSAIDA GALILEA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>RAZON</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,67 +1411,79 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6642581633</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>6692339589</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>C FERROCARRIL</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>02-01-1991</t>
+          <t>16-05-2002</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>JESUSLONSOASN@GMAIL.COM</t>
+          <t>GALIARIAS10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 21:34:11</t>
+          <t>03-03-2026 06:59:40</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 21:37:54</t>
+          <t>03-03-2026 07:03:01</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>03-03-2026 07:01:46</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1503,14 +1491,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26120522820940009167</t>
+          <t>26120522830980009202</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -1527,12 +1515,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347769</t>
+          <t>347444</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89934</t>
+          <t>89609</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1542,17 +1530,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VIRGEN ARLETT</t>
+          <t>VIVIAN ARLETH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>RENTERIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1562,12 +1550,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6631079402</t>
+          <t>6633288198</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>VALLE REDONDO MZ 3 LT 302</t>
+          <t>COL CERRO COL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1577,22 +1565,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22-01-2004</t>
+          <t>07-10-2005</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ARLETTPARRA8@GMAIL.COM</t>
+          <t>LILIANVALLES171@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:49:10</t>
+          <t>02-03-2026 08:32:44</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1602,7 +1590,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1612,7 +1600,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:58:07</t>
+          <t>02-03-2026 08:35:45</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1622,7 +1610,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 17:57:21</t>
+          <t>02-03-2026 08:34:41</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1632,7 +1620,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1642,7 +1630,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26120522809460009082</t>
+          <t>26120522784290008953</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1654,24 +1642,24 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aram Geronimo Garay Alvarado</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347652</t>
+          <t>347769</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89817</t>
+          <t>89934</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1681,17 +1669,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MARITZA DHENYS</t>
+          <t>VIRGEN ARLETT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LUGO</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1701,10 +1689,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6646939605</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>6631079402</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>VALLE REDONDO MZ 3 LT 302</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1712,42 +1704,42 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>15-10-2003</t>
+          <t>22-01-2004</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>MARITZASNACHEZ@GMAIL.COM</t>
+          <t>ARLETTPARRA8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 15:53:37</t>
+          <t>02-03-2026 17:49:10</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 15:55:09</t>
+          <t>02-03-2026 17:58:07</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1755,13 +1747,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:57:21</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1769,36 +1769,36 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26120522799140009047</t>
+          <t>26120522809460009082</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347751</t>
+          <t>347597</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89916</t>
+          <t>89762</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1808,17 +1808,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ALEJANDRA</t>
+          <t>BEATRIZ ELENA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SIGUENZA</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1828,14 +1828,10 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6643096129</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>PRIV GRANTE 3450 O 46</t>
-        </is>
-      </c>
+          <t>6631095288</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1843,38 +1839,42 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28-05-1980</t>
+          <t>12-06-1995</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MMENDOZASIGUENZA@GMAIL.COM</t>
+          <t>BAETRIZELENA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:34:49</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>02-03-2026 14:40:17</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (GRUPAL)</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 17:42:50</t>
+          <t>02-03-2026 14:41:19</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1882,21 +1882,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:41:55</t>
-        </is>
-      </c>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1904,14 +1896,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26120522807740009074</t>
+          <t>26120522795370009022</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1928,12 +1920,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347597</t>
+          <t>347437</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89762</t>
+          <t>89602</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1943,17 +1935,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BEATRIZ ELENA</t>
+          <t>LUIS ANGEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1963,28 +1955,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6631095288</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>6645735619</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>COND AZALOEA</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>12-06-1995</t>
+          <t>02-10-1995</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>BAETRIZELENA@GMAIL.COM</t>
+          <t>OCTUBRE95TG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 14:40:17</t>
+          <t>02-03-2026 08:13:46</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1994,22 +1990,22 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 14:41:19</t>
+          <t>02-03-2026 08:17:15</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2017,13 +2013,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>02-03-2026 08:16:13</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2031,19 +2035,19 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26120522795370009022</t>
+          <t>26120522783750008947</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>Aram Geronimo Garay Alvarado</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2055,12 +2059,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347722</t>
+          <t>347464</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89887</t>
+          <t>89629</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2070,17 +2074,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ESLY YUCARY</t>
+          <t>THELMA NOEMI</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ARIZMENDI</t>
+          <t>SALDIVAR</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ARCINIEGA</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2090,12 +2094,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6647796345</t>
+          <t>3441658484</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>VILLA DEL REAL</t>
+          <t>PRIV</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2105,42 +2109,42 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22-08-2000</t>
+          <t>15-12-1994</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>NICOLE726.H@GMAIL.COM</t>
+          <t>SALDIVARNOEMI07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:08:33</t>
+          <t>02-03-2026 09:26:02</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:57</t>
+          <t>02-03-2026 09:27:31</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2150,7 +2154,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:07</t>
+          <t>02-03-2026 09:27:12</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2170,36 +2174,36 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26120522805990009068</t>
+          <t>26120522785900008969</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347914</t>
+          <t>347652</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90079</t>
+          <t>89817</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2209,17 +2213,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FRIDA</t>
+          <t>MARITZA DHENYS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TREJO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>LUGO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2229,7 +2233,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6635910806</t>
+          <t>6646939605</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2240,17 +2244,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>24-03-1988</t>
+          <t>15-10-2003</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>FRIDAGSMAHS@GMAIL.COM</t>
+          <t>MARITZASNACHEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 21:39:35</t>
+          <t>02-03-2026 15:53:37</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2275,7 +2279,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 21:40:28</t>
+          <t>02-03-2026 15:55:09</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2297,7 +2301,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26120522820960009168</t>
+          <t>26120522799140009047</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2321,12 +2325,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347785</t>
+          <t>348173</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89950</t>
+          <t>90338</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2336,17 +2340,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PERLA ROSALBA</t>
+          <t>ESTEBAN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>URIBE</t>
+          <t>ARREOLA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2356,32 +2360,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6691277001</t>
+          <t>6645821899</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PRIV CAÑADADE LAS ACACIAS 22505 12</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>27-10-1998</t>
+          <t>26-06-2003</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>PERLARUR10@GMAIL.COM</t>
+          <t>ESTEBANARREOLASLOEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 18:00:10</t>
+          <t>03-03-2026 17:24:27</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2406,17 +2410,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 18:03:30</t>
+          <t>03-03-2026 17:29:05</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>02-03-2026 18:03:04</t>
+          <t>03-03-2026 17:28:40</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2426,7 +2430,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2436,7 +2440,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26120522809950009084</t>
+          <t>26120522850960009316</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2448,24 +2452,24 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347879</t>
+          <t>347963</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90044</t>
+          <t>90128</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2475,17 +2479,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA </t>
+          <t>DULCE YANET</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2495,12 +2499,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6631642692</t>
+          <t>6644919254</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>C ANTURIO 9513</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2510,52 +2514,52 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18-12-2001</t>
+          <t>06-09-1983</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ANDREASANCHEZSD@GMAIL.COM</t>
+          <t>DULCEGARAY327@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 19:44:09</t>
+          <t>03-03-2026 08:17:05</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 19:47:39</t>
+          <t>03-03-2026 08:23:39</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-03-2026 19:47:08</t>
+          <t>03-03-2026 08:22:58</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2565,7 +2569,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2575,14 +2579,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26120522817830009134</t>
+          <t>26120522833250009214</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2599,12 +2603,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347709</t>
+          <t>348255</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89874</t>
+          <t>90420</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2614,17 +2618,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BLANCA STEPHANIE</t>
+          <t xml:space="preserve">AYLINE </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>TERCERO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>DE LA ROSA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2634,14 +2638,10 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6658952135</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>6658952416</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2649,64 +2649,56 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>31-01-1996</t>
+          <t>18-08-2005</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BLANXASTEPHAIEES@GMAIL.COM</t>
+          <t>AYLINETERCEROS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 16:51:23</t>
+          <t>03-03-2026 19:10:06</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 16:56:27</t>
+          <t>03-03-2026 19:11:29</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:55:58</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2714,24 +2706,24 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26120522803950009062</t>
+          <t>26120522857830009348</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -3004,12 +2996,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347848</t>
+          <t>347709</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90013</t>
+          <t>89874</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3019,17 +3011,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DANIELA ANGELINA</t>
+          <t>BLANCA STEPHANIE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ARENAS</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3039,12 +3031,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6676627014</t>
+          <t>6658952135</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C DE LOS EUCALIPTOS MZ 32 LT 29 A</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3054,17 +3046,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>13-02-2003</t>
+          <t>31-01-1996</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>DANNI13ARENAS@GMAIL.COM</t>
+          <t>BLANXASTEPHAIEES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 18:43:33</t>
+          <t>02-03-2026 16:51:23</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3089,7 +3081,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 18:51:24</t>
+          <t>02-03-2026 16:56:27</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3099,7 +3091,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 18:50:43</t>
+          <t>02-03-2026 16:55:58</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3119,7 +3111,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26120522814230009112</t>
+          <t>26120522803950009062</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3131,12 +3123,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
@@ -3258,10 +3250,1209 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
+          <t>Juan Antonio  Beltran Sanchez</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>347914</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>90079</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>FRIDA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TREJO</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6635910806</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>24-03-1988</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>FRIDAGSMAHS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>02-03-2026 21:39:35</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>02-03-2026 21:40:28</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>26120522820960009168</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>347722</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>89887</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ESLY YUCARY</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ARIZMENDI</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ARCINIEGA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6647796345</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>VILLA DEL REAL</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>22-08-2000</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NICOLE726.H@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:08:33</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:19:57</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:19:07</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>26120522805990009068</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Leslie Camacho Murillo</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>347785</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>89950</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PERLA ROSALBA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>URIBE</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>RUIZ</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6691277001</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>PRIV CAÑADADE LAS ACACIAS 22505 12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>27-10-1998</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>PERLARUR10@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:00:10</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:03:30</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:03:04</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>26120522809950009084</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Leslie Camacho Murillo</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>347879</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>90044</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ANDREA </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>6631642692</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>18-12-2001</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>ANDREASANCHEZSD@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:44:09</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:47:39</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:47:08</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>26120522817830009134</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Leslie Camacho Murillo</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>347987</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>90152</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6197611989</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>28-07-1987</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>PEDROALVAREZ8728@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:24:18</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:25:49</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>26120522834820009220</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>347751</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>89916</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ALEJANDRA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SIGUENZA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6643096129</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>PRIV GRANTE 3450 O 46</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>28-05-1980</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>MMENDOZASIGUENZA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:34:49</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (GRUPAL)</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:42:50</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:41:55</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26120522807740009074</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Leslie Camacho Murillo</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>348073</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>90238</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>KAREN ALEXANDRA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BENITEZ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>VAZQUEZ</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6645821332</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>03-03-2000</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>HAMKARENSMD@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:01:24</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:02:44</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26120522842870009270</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>347848</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>90013</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DANIELA ANGELINA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ARENAS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6676627014</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>C DE LOS EUCALIPTOS MZ 32 LT 29 A</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>13-02-2003</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>DANNI13ARENAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:43:33</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:51:24</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:50:43</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26120522814230009112</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>348256</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>90421</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>JOSSELINE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TERCERO</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DELA ROSA</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>6645895152</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>28-10-1998</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>JOSSELINETERCEROS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:12:32</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:13:32</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26120522857990009349</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO 2000.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO 2000.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347432</t>
+          <t>282275</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89597</t>
+          <t>79776</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DANNA PAOLA</t>
+          <t>CRISTINA JOSELIN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ROMO</t>
+          <t>ALDRETE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VILLAFAÑA</t>
+          <t>CAMARILLO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6631048616</t>
+          <t>6645027425</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -624,22 +624,22 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20-08-2002</t>
+          <t>07-02-2009</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ROMODANNA@GMAIL.COM</t>
+          <t>CRISJAC@YAHOO.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>02-03-2026 08:00:32</t>
+          <t>08-03-2025 09:37:53</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -649,22 +649,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 08:01:52</t>
+          <t>03-03-2026 15:22:07</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -681,14 +681,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26120522783320008941</t>
+          <t>26120522843690009284</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>282275</t>
+          <t>265886</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79776</t>
+          <t>63390</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CRISTINA JOSELIN</t>
+          <t xml:space="preserve">MARTIZA </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ALDRETE</t>
+          <t>BLANCARTE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CAMARILLO</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,10 +740,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6645027425</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>6645955683</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -751,42 +755,42 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>07-02-2009</t>
+          <t>08-06-1997</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CRISJAC@YAHOO.COM</t>
+          <t>08.MARITZAB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>08-03-2025 09:37:53</t>
+          <t>12-11-2024 13:28:20</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 15:22:07</t>
+          <t>03-03-2026 20:34:26</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -794,13 +798,21 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>03-03-2026 20:31:06</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -808,14 +820,14 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26120522843690009284</t>
+          <t>26120522861150009379</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -832,12 +844,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347405</t>
+          <t>119316</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89570</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,17 +859,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ITZEL KARINA</t>
+          <t>FABIOLA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GAXIOLA</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -867,12 +879,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6647511082</t>
+          <t>9631161801</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BOCA DELOBO</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -882,22 +894,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>04-01-2005</t>
+          <t>27-06-1978</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>KGAXIOLA51@GMAIL.COM</t>
+          <t>REHGWSERT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>02-03-2026 06:37:04</t>
+          <t>29-08-2022 20:34:45</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -907,7 +919,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -917,17 +929,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>02-03-2026 06:39:25</t>
+          <t>05-03-2026 20:20:37</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>02-03-2026 06:38:46</t>
+          <t>05-03-2026 20:20:16</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -937,7 +949,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -947,7 +959,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26120522780920008926</t>
+          <t>26120522931250009803</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -959,24 +971,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Kevin Uriel  Aguilar Dionisio</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347441</t>
+          <t>347405</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89606</t>
+          <t>89570</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -986,17 +998,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RAUL DUARDO</t>
+          <t>ITZEL KARINA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>GAXIOLA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OSORNIO</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1006,32 +1018,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6648202291</t>
+          <t>6647511082</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C HDA SAN MIGUEL</t>
+          <t>BOCA DELOBO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>15-11-2003</t>
+          <t>04-01-2005</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>TORRESRAUL383@GMAIL.COM</t>
+          <t>KGAXIOLA51@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 08:26:25</t>
+          <t>02-03-2026 06:37:04</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1056,7 +1068,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 08:29:25</t>
+          <t>02-03-2026 06:39:25</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1066,7 +1078,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 08:29:09</t>
+          <t>02-03-2026 06:38:46</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1086,7 +1098,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26120522784170008951</t>
+          <t>26120522780920008926</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1098,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Aram Geronimo Garay Alvarado</t>
+          <t>Kevin Uriel  Aguilar Dionisio</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1110,12 +1122,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>265886</t>
+          <t>347441</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>63390</t>
+          <t>89606</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1125,17 +1137,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTIZA </t>
+          <t>RAUL DUARDO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BLANCARTE</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>OSORNIO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1145,32 +1157,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6645955683</t>
+          <t>6648202291</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>C HDA SAN MIGUEL</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>08-06-1997</t>
+          <t>15-11-2003</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>08.MARITZAB@GMAIL.COM</t>
+          <t>TORRESRAUL383@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12-11-2024 13:28:20</t>
+          <t>02-03-2026 08:26:25</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1180,32 +1192,32 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 20:34:26</t>
+          <t>02-03-2026 08:29:25</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-03-2026 20:31:06</t>
+          <t>02-03-2026 08:29:09</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1225,36 +1237,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26120522861150009379</t>
+          <t>26120522784170008951</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aram Geronimo Garay Alvarado</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347913</t>
+          <t>347444</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90078</t>
+          <t>89609</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,17 +1276,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>JESUS ALONSO</t>
+          <t>VIVIAN ARLETH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>RENTERIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1284,28 +1296,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6642581633</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>6633288198</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>COL CERRO COL</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>02-01-1991</t>
+          <t>07-10-2005</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>JESUSLONSOASN@GMAIL.COM</t>
+          <t>LILIANVALLES171@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 21:34:11</t>
+          <t>02-03-2026 08:32:44</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1315,22 +1331,22 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 21:37:54</t>
+          <t>02-03-2026 08:35:45</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1338,13 +1354,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>02-03-2026 08:34:41</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1352,36 +1376,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26120522820940009167</t>
+          <t>26120522784290008953</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aram Geronimo Garay Alvarado</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347942</t>
+          <t>347416</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>90107</t>
+          <t>89581</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1391,17 +1415,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BETSAIDA GALILEA</t>
+          <t xml:space="preserve">FERNANDA </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>CORDERO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>RAZON</t>
+          <t>GAMEZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1411,12 +1435,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6692339589</t>
+          <t>6644066474</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C FERROCARRIL</t>
+          <t>PRIV</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1426,17 +1450,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>16-05-2002</t>
+          <t>25-12-2004</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>GALIARIAS10@GMAIL.COM</t>
+          <t>FERNANDAC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>03-03-2026 06:59:40</t>
+          <t>02-03-2026 07:19:38</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1461,17 +1485,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 07:03:01</t>
+          <t>04-03-2026 07:16:47</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-03-2026 07:01:46</t>
+          <t>04-03-2026 07:16:17</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1491,10 +1515,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26120522830980009202</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26120522873910009433</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1503,24 +1531,24 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Uriel  Aguilar Dionisio</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347444</t>
+          <t>221623</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89609</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1530,17 +1558,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VIVIAN ARLETH</t>
+          <t xml:space="preserve">MARIA DE JESUS </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>RENTERIA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1550,12 +1578,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6633288198</t>
+          <t>6648258475</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COL CERRO COL</t>
+          <t>C LOMAS DEL RIO MZ LT 8 FRACC LOMAS DEL VALLE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1565,22 +1593,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>07-10-2005</t>
+          <t>25-02-1999</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>LILIANVALLES171@GMAIL.COM</t>
+          <t>MP178146@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 08:32:44</t>
+          <t>26-02-2024 13:55:44</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1590,7 +1618,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1600,17 +1628,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 08:35:45</t>
+          <t>05-03-2026 12:02:32</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 08:34:41</t>
+          <t>05-03-2026 12:01:48</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1630,7 +1658,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26120522784290008953</t>
+          <t>26070522914140004762</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1642,7 +1670,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Aram Geronimo Garay Alvarado</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1654,12 +1682,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347769</t>
+          <t>344964</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89934</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1669,17 +1697,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VIRGEN ARLETT</t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>NOTARIO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1689,47 +1717,43 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6631079402</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>VALLE REDONDO MZ 3 LT 302</t>
-        </is>
-      </c>
+          <t>9622967203</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22-01-2004</t>
+          <t>16-03-1995</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ARLETTPARRA8@GMAIL.COM</t>
+          <t>JUANMANUELABDMJS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>02-03-2026 17:49:10</t>
+          <t>18-02-2026 20:42:39</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1739,29 +1763,21 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 17:58:07</t>
+          <t>04-03-2026 20:58:03</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:57:21</t>
-        </is>
-      </c>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1769,10 +1785,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26120522809460009082</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
+          <t>26120522899970009616</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1781,24 +1801,24 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347597</t>
+          <t>347963</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89762</t>
+          <t>90128</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1808,17 +1828,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BEATRIZ ELENA</t>
+          <t>DULCE YANET</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>GARAY</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>OSUNA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1828,10 +1848,14 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6631095288</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>6644919254</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>C ANTURIO 9513</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1839,17 +1863,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>12-06-1995</t>
+          <t>06-09-1983</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>BAETRIZELENA@GMAIL.COM</t>
+          <t>DULCEGARAY327@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 14:40:17</t>
+          <t>03-03-2026 08:17:05</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1859,36 +1883,44 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 14:41:19</t>
+          <t>03-03-2026 08:23:39</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:22:58</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1896,24 +1928,24 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26120522795370009022</t>
+          <t>26120522833250009214</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
@@ -2198,12 +2230,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347652</t>
+          <t>347471</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89817</t>
+          <t>89636</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2213,17 +2245,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MARITZA DHENYS</t>
+          <t>VICTOR HUGO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>PEREIRA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LUGO</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2233,33 +2265,33 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6646939605</t>
+          <t>6642222176</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>15-10-2003</t>
+          <t>05-12-2002</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>MARITZASNACHEZ@GMAIL.COM</t>
+          <t>VICTORHUGO002@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 15:53:37</t>
+          <t>02-03-2026 09:49:28</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2269,17 +2301,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 15:55:09</t>
+          <t>02-03-2026 09:50:47</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2301,36 +2333,36 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26120522799140009047</t>
+          <t>26120522786620008980</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Uriel  Aguilar Dionisio</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>348173</t>
+          <t>347769</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90338</t>
+          <t>89934</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2340,17 +2372,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ESTEBAN</t>
+          <t>VIRGEN ARLETT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ARREOLA</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2360,32 +2392,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6645821899</t>
+          <t>6631079402</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>VALLE REDONDO MZ 3 LT 302</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>26-06-2003</t>
+          <t>22-01-2004</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ESTEBANARREOLASLOEZ@GMAIL.COM</t>
+          <t>ARLETTPARRA8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 17:24:27</t>
+          <t>02-03-2026 17:49:10</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2410,17 +2442,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 17:29:05</t>
+          <t>02-03-2026 17:58:07</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>03-03-2026 17:28:40</t>
+          <t>02-03-2026 17:57:21</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2430,7 +2462,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2440,7 +2472,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26120522850960009316</t>
+          <t>26120522809460009082</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2464,12 +2496,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347963</t>
+          <t>347597</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>90128</t>
+          <t>89762</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2479,17 +2511,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DULCE YANET</t>
+          <t>BEATRIZ ELENA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2499,14 +2531,10 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6644919254</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>C ANTURIO 9513</t>
-        </is>
-      </c>
+          <t>6631095288</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2514,17 +2542,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>06-09-1983</t>
+          <t>12-06-1995</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>DULCEGARAY327@GMAIL.COM</t>
+          <t>BAETRIZELENA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>03-03-2026 08:17:05</t>
+          <t>02-03-2026 14:40:17</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2534,44 +2562,36 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>03-03-2026 08:23:39</t>
+          <t>02-03-2026 14:41:19</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>03-03-2026 08:22:58</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2579,36 +2599,36 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26120522833250009214</t>
+          <t>26120522795370009022</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>348255</t>
+          <t>347722</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90420</t>
+          <t>89887</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2618,17 +2638,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">AYLINE </t>
+          <t>ESLY YUCARY</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TERCERO</t>
+          <t>ARIZMENDI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DE LA ROSA</t>
+          <t>ARCINIEGA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2638,10 +2658,14 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6658952416</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>6647796345</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>VILLA DEL REAL</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2649,56 +2673,64 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18-08-2005</t>
+          <t>22-08-2000</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>AYLINETERCEROS@GMAIL.COM</t>
+          <t>NICOLE726.H@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>03-03-2026 19:10:06</t>
+          <t>02-03-2026 17:08:33</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>03-03-2026 19:11:29</t>
+          <t>02-03-2026 17:19:57</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:19:07</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2706,36 +2738,36 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26120522857830009348</t>
+          <t>26120522805990009068</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347471</t>
+          <t>347785</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89636</t>
+          <t>89950</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2745,17 +2777,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VICTOR HUGO</t>
+          <t>PERLA ROSALBA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PEREIRA</t>
+          <t>URIBE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2765,43 +2797,47 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6642222176</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>6691277001</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>PRIV CAÑADADE LAS ACACIAS 22505 12</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>05-12-2002</t>
+          <t>27-10-1998</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>VICTORHUGO002@GMAIL.COM</t>
+          <t>PERLARUR10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 09:49:28</t>
+          <t>02-03-2026 18:00:10</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2811,7 +2847,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 09:50:47</t>
+          <t>02-03-2026 18:03:30</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2819,13 +2855,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:03:04</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2833,7 +2877,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26120522786620008980</t>
+          <t>26120522809950009084</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2845,7 +2889,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Kevin Uriel  Aguilar Dionisio</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2857,12 +2901,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347614</t>
+          <t>347432</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89779</t>
+          <t>89597</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2872,17 +2916,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KAREN ISABEL</t>
+          <t>DANNA PAOLA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ROMO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>VILLAFAÑA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2892,14 +2936,10 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6864237953</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>6631048616</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2907,17 +2947,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>07-08-1994</t>
+          <t>20-08-2002</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>KARENISABELRAMTEZ@GMAIL.COM</t>
+          <t>ROMODANNA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 15:02:53</t>
+          <t>02-03-2026 08:00:32</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2927,22 +2967,22 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 15:05:09</t>
+          <t>02-03-2026 08:01:52</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2950,21 +2990,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>02-03-2026 15:04:45</t>
-        </is>
-      </c>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2972,36 +3004,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26120522796430009035</t>
+          <t>26120522783320008941</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Juan Antonio  Beltran Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347709</t>
+          <t>348255</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89874</t>
+          <t>90420</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3011,17 +3043,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BLANCA STEPHANIE</t>
+          <t xml:space="preserve">AYLINE </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>TERCERO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>DE LA ROSA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3031,14 +3063,10 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6658952135</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>6658952416</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3046,64 +3074,56 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31-01-1996</t>
+          <t>18-08-2005</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BLANXASTEPHAIEES@GMAIL.COM</t>
+          <t>AYLINETERCEROS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 16:51:23</t>
+          <t>03-03-2026 19:10:06</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 16:56:27</t>
+          <t>03-03-2026 19:11:29</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:55:58</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3111,36 +3131,36 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26120522803950009062</t>
+          <t>26120522857830009348</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347874</t>
+          <t>348391</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90039</t>
+          <t>90556</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3150,17 +3170,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PERLA</t>
+          <t>ALEJANDRO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>URIBE</t>
+          <t>NESTA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>PUERTOS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3170,67 +3190,79 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6643349799</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>6631628130</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AV PLATA</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>12-12-2007</t>
+          <t>15-11-1988</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PERLAURIBEPASTEL@GMAIL.COM</t>
+          <t>ALEJANDRONESTA60@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 19:40:22</t>
+          <t>04-03-2026 11:17:53</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-03-2026 19:42:36</t>
+          <t>04-03-2026 11:26:01</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>04-03-2026 11:19:46</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3238,36 +3270,36 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26120522817540009133</t>
+          <t>26120522879420009479</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Juan Antonio  Beltran Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347914</t>
+          <t>347652</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90079</t>
+          <t>89817</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3277,17 +3309,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FRIDA</t>
+          <t>MARITZA DHENYS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TREJO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>LUGO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3297,7 +3329,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6635910806</t>
+          <t>6646939605</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3308,17 +3340,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>24-03-1988</t>
+          <t>15-10-2003</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>FRIDAGSMAHS@GMAIL.COM</t>
+          <t>MARITZASNACHEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-03-2026 21:39:35</t>
+          <t>02-03-2026 15:53:37</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3343,7 +3375,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-03-2026 21:40:28</t>
+          <t>02-03-2026 15:55:09</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3365,7 +3397,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26120522820960009168</t>
+          <t>26120522799140009047</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3389,12 +3421,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347722</t>
+          <t>347751</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89887</t>
+          <t>89916</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3404,17 +3436,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ESLY YUCARY</t>
+          <t>ALEJANDRA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ARIZMENDI</t>
+          <t>SIGUENZA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ARCINIEGA</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3424,12 +3456,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6647796345</t>
+          <t>6643096129</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>VILLA DEL REAL</t>
+          <t>PRIV GRANTE 3450 O 46</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3439,24 +3471,20 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>22-08-2000</t>
+          <t>28-05-1980</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>NICOLE726.H@GMAIL.COM</t>
+          <t>MMENDOZASIGUENZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 17:08:33</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Inscripcion $150</t>
-        </is>
-      </c>
+          <t>02-03-2026 17:34:49</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -3464,17 +3492,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (GRUPAL)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:57</t>
+          <t>02-03-2026 17:42:50</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3484,7 +3512,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:07</t>
+          <t>02-03-2026 17:41:55</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3504,14 +3532,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26120522805990009068</t>
+          <t>26120522807740009074</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3528,12 +3556,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347785</t>
+          <t>347614</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89950</t>
+          <t>89779</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3543,17 +3571,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PERLA ROSALBA</t>
+          <t>KAREN ISABEL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>URIBE</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3563,12 +3591,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6691277001</t>
+          <t>6864237953</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PRIV CAÑADADE LAS ACACIAS 22505 12</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3578,42 +3606,42 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>27-10-1998</t>
+          <t>07-08-1994</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PERLARUR10@GMAIL.COM</t>
+          <t>KARENISABELRAMTEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:00:10</t>
+          <t>02-03-2026 15:02:53</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:03:30</t>
+          <t>02-03-2026 15:05:09</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3623,7 +3651,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:03:04</t>
+          <t>02-03-2026 15:04:45</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3643,19 +3671,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26120522809950009084</t>
+          <t>26120522796430009035</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>Juan Antonio  Beltran Sanchez</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3667,12 +3695,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347879</t>
+          <t>347914</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90044</t>
+          <t>90079</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3682,17 +3710,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA </t>
+          <t>FRIDA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>TREJO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3702,14 +3730,10 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6631642692</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>6635910806</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3717,42 +3741,42 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>18-12-2001</t>
+          <t>24-03-1988</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ANDREASANCHEZSD@GMAIL.COM</t>
+          <t>FRIDAGSMAHS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 19:44:09</t>
+          <t>02-03-2026 21:39:35</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-03-2026 19:47:39</t>
+          <t>02-03-2026 21:40:28</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3760,21 +3784,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:47:08</t>
-        </is>
-      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3782,36 +3798,36 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26120522817830009134</t>
+          <t>26120522820960009168</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347987</t>
+          <t>348196</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90152</t>
+          <t>90361</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3821,53 +3837,53 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PEDRO</t>
+          <t>EDGAR ANDRES</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>GOMARA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6197611989</t>
+          <t>6642267630</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>28-07-1987</t>
+          <t>30-03-2008</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>PEDROALVAREZ8728@GMAIL.COM</t>
+          <t>GOMARAEDGAR57@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>03-03-2026 09:24:18</t>
+          <t>03-03-2026 17:52:01</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3877,28 +3893,28 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>03-03-2026 09:25:49</t>
+          <t>04-03-2026 19:57:53</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -3909,14 +3925,18 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26120522834820009220</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
+          <t>26120522898580009603</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -3933,12 +3953,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>347751</t>
+          <t>310500</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>89916</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3948,17 +3968,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ALEJANDRA</t>
+          <t>KAREN VIANEY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SIGUENZA</t>
+          <t>CUELLAR</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3968,12 +3988,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6643096129</t>
+          <t>6643280099</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PRIV GRANTE 3450 O 46</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3983,20 +4003,24 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>28-05-1980</t>
+          <t>01-08-2004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>MMENDOZASIGUENZA@GMAIL.COM</t>
+          <t>VIANEYCUELLAR22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-03-2026 17:34:49</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>21-08-2025 05:35:54</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t>Forzoso</t>
@@ -4004,27 +4028,27 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (GRUPAL)</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-03-2026 17:42:50</t>
+          <t>05-03-2026 18:20:20</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-03-2026 17:41:55</t>
+          <t>05-03-2026 18:19:44</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4044,36 +4068,36 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26120522807740009074</t>
+          <t>26120522926720009755</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>348073</t>
+          <t>347879</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90238</t>
+          <t>90044</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4083,17 +4107,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KAREN ALEXANDRA</t>
+          <t xml:space="preserve">ANDREA </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BENITEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4103,43 +4127,47 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6645821332</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>6631642692</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>03-03-2000</t>
+          <t>18-12-2001</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>HAMKARENSMD@GMAIL.COM</t>
+          <t>ANDREASANCHEZSD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>03-03-2026 15:01:24</t>
+          <t>02-03-2026 19:44:09</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4149,21 +4177,29 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>03-03-2026 15:02:44</t>
+          <t>02-03-2026 19:47:39</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr"/>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:47:08</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4171,7 +4207,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26120522842870009270</t>
+          <t>26120522817830009134</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4183,24 +4219,24 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347848</t>
+          <t>347987</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90013</t>
+          <t>90152</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4210,34 +4246,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DANIELA ANGELINA</t>
+          <t>PEDRO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ARENAS</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6676627014</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>C DE LOS EUCALIPTOS MZ 32 LT 29 A</t>
-        </is>
-      </c>
+          <t>6197611989</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4245,64 +4277,56 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>13-02-2003</t>
+          <t>28-07-1987</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>DANNI13ARENAS@GMAIL.COM</t>
+          <t>PEDROALVAREZ8728@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-03-2026 18:43:33</t>
+          <t>03-03-2026 09:24:18</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-03-2026 18:51:24</t>
+          <t>03-03-2026 09:25:49</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:50:43</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4310,14 +4334,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26120522814230009112</t>
+          <t>26120522834820009220</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4334,12 +4358,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>348256</t>
+          <t>348073</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90421</t>
+          <t>90238</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4349,17 +4373,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JOSSELINE GUADALUPE</t>
+          <t>KAREN ALEXANDRA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>TERCERO</t>
+          <t>BENITEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DELA ROSA</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4369,33 +4393,33 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6645895152</t>
+          <t>6645821332</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>28-10-1998</t>
+          <t>03-03-2000</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>JOSSELINETERCEROS@GMAIL.COM</t>
+          <t>HAMKARENSMD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>03-03-2026 19:12:32</t>
+          <t>03-03-2026 15:01:24</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -4405,17 +4429,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>03-03-2026 19:13:32</t>
+          <t>03-03-2026 15:02:44</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -4437,22 +4461,1785 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26120522857990009349</t>
+          <t>26120522842870009270</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>347709</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>89874</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BLANCA STEPHANIE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ARELLANO</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6658952135</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>31-01-1996</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>BLANXASTEPHAIEES@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:51:23</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:56:27</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:55:58</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26120522803950009062</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Leslie Camacho Murillo</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>347874</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>90039</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PERLA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>URIBE</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6643349799</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>12-12-2007</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>PERLAURIBEPASTEL@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:40:22</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:42:36</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26120522817540009133</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Juan Antonio  Beltran Sanchez</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>347913</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>90078</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>JESUS ALONSO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>GOMEZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>6642581633</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>02-01-1991</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>JESUSLONSOASN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>02-03-2026 21:34:11</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>02-03-2026 21:37:54</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26120522820940009167</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>347942</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>90107</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BETSAIDA GALILEA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ARIAS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>RAZON</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>6692339589</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>C FERROCARRIL</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>16-05-2002</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>GALIARIAS10@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>03-03-2026 06:59:40</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>03-03-2026 07:03:01</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>03-03-2026 07:01:46</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26120522830980009202</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Kevin Uriel  Aguilar Dionisio</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>347848</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>90013</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DANIELA ANGELINA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ARENAS</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>6676627014</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>C DE LOS EUCALIPTOS MZ 32 LT 29 A</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>13-02-2003</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>DANNI13ARENAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:43:33</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:51:24</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:50:43</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26120522814230009112</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>347419</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>89584</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIS FERNANDO </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DIAZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SEGURA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>6647879129</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>PRIV</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>22-08-2000</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>LUISFERNANDO11@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>02-03-2026 07:22:04</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:19:12</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:18:37</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26120522874040009434</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Kevin Uriel  Aguilar Dionisio</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>348542</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>90707</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>JOSEFINA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>6646659961</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>19-03-1984</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>JOSEFINASDA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:51:53</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:56:02</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:53:44</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26120522892320009556</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Juan Antonio  Beltran Sanchez</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>348173</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>90338</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ESTEBAN</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ARREOLA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>6645821899</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>26-06-2003</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>ESTEBANARREOLASLOEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:24:27</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:29:05</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:28:40</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26120522850960009316</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Leslie Camacho Murillo</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>348638</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>90803</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NOVEYDA YANETH</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>MONZON</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>6647451798</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>CTO REAL PEDREGAL</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>01-12-1987</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>YANETHMORENO8484@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>05-03-2026 09:03:06</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>05-03-2026 09:06:16</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>05-03-2026 09:05:19</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26120522911300009657</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>348256</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>90421</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>JOSSELINE GUADALUPE</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>TERCERO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>DELA ROSA</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>6645895152</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>28-10-1998</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>JOSSELINETERCEROS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:12:32</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:13:32</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26120522857990009349</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>348393</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>90558</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KAREN </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DE JORGE</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>6642656887</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>PRIV</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>20-10-1991</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>KARENDEJORGE093@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>04-03-2026 11:28:01</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>04-03-2026 11:30:00</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>04-03-2026 11:29:08</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26120522879500009480</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>348812</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>90977</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LUCERO ESTEFANIA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>NAVARRETE</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SOLIS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6658954251</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>19-01-1993</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>UCOERISNAVARRETE@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:14:48</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:18:18</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>05-03-2026 20:17:40</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26120522931180009800</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>348383</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>90548</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>OSWALDO</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ARVIZU</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>6645743473</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>19-08-2004</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>OSWALDO.SANCHEZ@UABC.EDU.MX</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:40:25</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Convenio 99</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>CONVENIOS $549</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>04-03-2026 10:41:47</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26120522878810009472</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO 2000.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__PASEO 2000.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC43"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>282275</t>
+          <t>310500</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>79776</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRISTINA JOSELIN</t>
+          <t>KAREN VIANEY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ALDRETE</t>
+          <t>CUELLAR</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CAMARILLO</t>
+          <t>JUAREZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,10 +613,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6645027425</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>6643280099</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -624,32 +628,32 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>07-02-2009</t>
+          <t>01-08-2004</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CRISJAC@YAHOO.COM</t>
+          <t>VIANEYCUELLAR22@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>08-03-2025 09:37:53</t>
+          <t>21-08-2025 05:35:54</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -659,21 +663,29 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>03-03-2026 15:22:07</t>
+          <t>05-03-2026 18:20:20</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr"/>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>05-03-2026 18:19:44</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -681,7 +693,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26120522843690009284</t>
+          <t>26120522926720009755</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -705,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>265886</t>
+          <t>119316</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63390</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -720,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTIZA </t>
+          <t>FABIOLA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BLANCARTE</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BAUTISTA</t>
+          <t>NAVARRETE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -740,12 +752,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6645955683</t>
+          <t>9631161801</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -755,52 +767,52 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>08-06-1997</t>
+          <t>27-06-1978</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>08.MARITZAB@GMAIL.COM</t>
+          <t>REHGWSERT@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12-11-2024 13:28:20</t>
+          <t>29-08-2022 20:34:45</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>03-03-2026 20:34:26</t>
+          <t>05-03-2026 20:20:37</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>03-03-2026 20:31:06</t>
+          <t>05-03-2026 20:20:16</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -810,7 +822,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -820,36 +832,36 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26120522861150009379</t>
+          <t>26120522931250009803</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>119316</t>
+          <t>221623</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17023</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,17 +871,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FABIOLA</t>
+          <t xml:space="preserve">MARIA DE JESUS </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NAVARRETE</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -879,12 +891,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9631161801</t>
+          <t>6648258475</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>C LOMAS DEL RIO MZ LT 8 FRACC LOMAS DEL VALLE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -894,17 +906,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>27-06-1978</t>
+          <t>25-02-1999</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>REHGWSERT@GMAIL.COM</t>
+          <t>MP178146@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>29-08-2022 20:34:45</t>
+          <t>26-02-2024 13:55:44</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -929,17 +941,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>05-03-2026 20:20:37</t>
+          <t>05-03-2026 12:02:32</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>05-03-2026 20:20:16</t>
+          <t>05-03-2026 12:01:48</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -949,7 +961,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -959,7 +971,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26120522931250009803</t>
+          <t>26070522914140004762</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -971,24 +983,24 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Ivan Alberto  Nuñez Sanchez</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347405</t>
+          <t>337541</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89570</t>
+          <t>15360</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -998,17 +1010,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ITZEL KARINA</t>
+          <t>JOSE FELIX</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GAXIOLA</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>ESPIRITU</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1018,37 +1030,37 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6647511082</t>
+          <t>7471318775</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BOCA DELOBO</t>
+          <t>LA MORITA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>04-01-2005</t>
+          <t>14-07-2005</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>KGAXIOLA51@GMAIL.COM</t>
+          <t>HERNANDEZJOSEFELIX@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>02-03-2026 06:37:04</t>
+          <t>24-01-2026 12:46:10</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1058,7 +1070,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1068,17 +1080,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 06:39:25</t>
+          <t>08-03-2026 13:11:38</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>07-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 06:38:46</t>
+          <t>08-03-2026 13:11:07</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1098,10 +1110,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26120522780920008926</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26110522986730004948</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1110,24 +1126,24 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Kevin Uriel  Aguilar Dionisio</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347441</t>
+          <t>265886</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89606</t>
+          <t>63390</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1137,17 +1153,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>RAUL DUARDO</t>
+          <t xml:space="preserve">MARTIZA </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>BLANCARTE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OSORNIO</t>
+          <t>BAUTISTA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1157,32 +1173,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6648202291</t>
+          <t>6645955683</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C HDA SAN MIGUEL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>15-11-2003</t>
+          <t>08-06-1997</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>TORRESRAUL383@GMAIL.COM</t>
+          <t>08.MARITZAB@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>02-03-2026 08:26:25</t>
+          <t>12-11-2024 13:28:20</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1192,22 +1208,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 08:29:25</t>
+          <t>03-03-2026 20:34:26</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1217,7 +1233,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 08:29:09</t>
+          <t>03-03-2026 20:31:06</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1237,36 +1253,36 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26120522784170008951</t>
+          <t>26120522861150009379</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Aram Geronimo Garay Alvarado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347444</t>
+          <t>287045</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89609</t>
+          <t>84543</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,17 +1292,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VIVIAN ARLETH</t>
+          <t xml:space="preserve">STACY </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VALLES</t>
+          <t>KAUWOH</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>RENTERIA</t>
+          <t>CUEVAS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1296,12 +1312,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6633288198</t>
+          <t>6641191721</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COL CERRO COL</t>
+          <t>LA MORITA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1311,22 +1327,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>07-10-2005</t>
+          <t>25-12-1992</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>LILIANVALLES171@GMAIL.COM</t>
+          <t>STACYKAUWOH17@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>02-03-2026 08:32:44</t>
+          <t>08-04-2025 13:10:24</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1336,7 +1352,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1346,17 +1362,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 08:35:45</t>
+          <t>07-03-2026 12:32:15</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>06-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 08:34:41</t>
+          <t>07-03-2026 12:30:40</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1376,7 +1392,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26120522784290008953</t>
+          <t>26120522974980010064</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1388,7 +1404,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Aram Geronimo Garay Alvarado</t>
+          <t>Kevin Uriel  Aguilar Dionisio</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1400,12 +1416,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>347416</t>
+          <t>347432</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>89581</t>
+          <t>89597</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1415,17 +1431,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FERNANDA </t>
+          <t>DANNA PAOLA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CORDERO</t>
+          <t>ROMO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GAMEZ</t>
+          <t>VILLAFAÑA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1435,14 +1451,10 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6644066474</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>PRIV</t>
-        </is>
-      </c>
+          <t>6631048616</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -1450,64 +1462,56 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>25-12-2004</t>
+          <t>20-08-2002</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FERNANDAC@GMAIL.COM</t>
+          <t>ROMODANNA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>02-03-2026 07:19:38</t>
+          <t>02-03-2026 08:00:32</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>04-03-2026 07:16:47</t>
+          <t>02-03-2026 08:01:52</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>04-03-2026 07:16:17</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1515,40 +1519,36 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26120522873910009433</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26120522783320008941</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Kevin Uriel  Aguilar Dionisio</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>221623</t>
+          <t>347437</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19130</t>
+          <t>89602</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARIA DE JESUS </t>
+          <t>LUIS ANGEL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1578,37 +1578,37 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6648258475</t>
+          <t>6645735619</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C LOMAS DEL RIO MZ LT 8 FRACC LOMAS DEL VALLE</t>
+          <t>COND AZALOEA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>25-02-1999</t>
+          <t>02-10-1995</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MP178146@GMAIL.COM</t>
+          <t>OCTUBRE95TG@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>26-02-2024 13:55:44</t>
+          <t>02-03-2026 08:13:46</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>05-03-2026 12:02:32</t>
+          <t>02-03-2026 08:17:15</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>05-03-2026 12:01:48</t>
+          <t>02-03-2026 08:16:13</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26070522914140004762</t>
+          <t>26120522783750008947</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Ivan Alberto  Nuñez Sanchez</t>
+          <t>Aram Geronimo Garay Alvarado</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>344964</t>
+          <t>347464</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22781</t>
+          <t>89629</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JUAN MANUEL</t>
+          <t>THELMA NOEMI</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SALDIVAR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NOTARIO</t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1717,67 +1717,79 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9622967203</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>3441658484</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PRIV</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>16-03-1995</t>
+          <t>15-12-1994</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>JUANMANUELABDMJS@GMAIL.COM</t>
+          <t>SALDIVARNOEMI07@GMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>18-02-2026 20:42:39</t>
+          <t>02-03-2026 09:26:02</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-03-2026 20:58:03</t>
+          <t>02-03-2026 09:27:31</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02-03-2026 09:27:12</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -1785,18 +1797,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26120522899970009616</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26120522785900008969</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1813,12 +1821,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347963</t>
+          <t>347416</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90128</t>
+          <t>89581</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1828,17 +1836,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DULCE YANET</t>
+          <t xml:space="preserve">FERNANDA </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GARAY</t>
+          <t>CORDERO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OSUNA</t>
+          <t>GAMEZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1848,12 +1856,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6644919254</t>
+          <t>6644066474</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C ANTURIO 9513</t>
+          <t>PRIV</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1863,42 +1871,42 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>06-09-1983</t>
+          <t>25-12-2004</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>DULCEGARAY327@GMAIL.COM</t>
+          <t>FERNANDAC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>03-03-2026 08:17:05</t>
+          <t>02-03-2026 07:19:38</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>03-03-2026 08:23:39</t>
+          <t>04-03-2026 07:16:47</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1908,7 +1916,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>03-03-2026 08:22:58</t>
+          <t>04-03-2026 07:16:17</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1918,7 +1926,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1928,36 +1936,40 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26120522833250009214</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
+          <t>26120522873910009433</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Kevin Uriel  Aguilar Dionisio</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>347437</t>
+          <t>344964</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89602</t>
+          <t>22781</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1967,17 +1979,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LUIS ANGEL</t>
+          <t>JUAN MANUEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PEREZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>NOTARIO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1987,14 +1999,10 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6645735619</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>COND AZALOEA</t>
-        </is>
-      </c>
+          <t>9622967203</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2002,32 +2010,32 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>02-10-1995</t>
+          <t>16-03-1995</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>OCTUBRE95TG@GMAIL.COM</t>
+          <t>JUANMANUELABDMJS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>02-03-2026 08:13:46</t>
+          <t>18-02-2026 20:42:39</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -2037,29 +2045,21 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 08:17:15</t>
+          <t>04-03-2026 20:58:03</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>02-03-2026 08:16:13</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2067,10 +2067,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26120522783750008947</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26120522899970009616</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2079,24 +2083,24 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Aram Geronimo Garay Alvarado</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347464</t>
+          <t>282275</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89629</t>
+          <t>79776</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2106,17 +2110,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>THELMA NOEMI</t>
+          <t>CRISTINA JOSELIN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SALDIVAR</t>
+          <t>ALDRETE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>CAMARILLO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2126,14 +2130,10 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3441658484</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>PRIV</t>
-        </is>
-      </c>
+          <t>6645027425</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2141,42 +2141,42 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>15-12-1994</t>
+          <t>07-02-2009</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>SALDIVARNOEMI07@GMAIL.COM</t>
+          <t>CRISJAC@YAHOO.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 09:26:02</t>
+          <t>08-03-2025 09:37:53</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 09:27:31</t>
+          <t>03-03-2026 15:22:07</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2184,21 +2184,13 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>02-03-2026 09:27:12</t>
-        </is>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2206,14 +2198,14 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26120522785900008969</t>
+          <t>26120522843690009284</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2230,12 +2222,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347471</t>
+          <t>347419</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89636</t>
+          <t>89584</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2245,17 +2237,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VICTOR HUGO</t>
+          <t xml:space="preserve">LUIS FERNANDO </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PEREIRA</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>SEGURA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2265,10 +2257,14 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6642222176</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>6647879129</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>PRIV</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -2276,32 +2272,32 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>05-12-2002</t>
+          <t>22-08-2000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>VICTORHUGO002@GMAIL.COM</t>
+          <t>LUISFERNANDO11@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 09:49:28</t>
+          <t>02-03-2026 07:22:04</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2311,21 +2307,29 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 09:50:47</t>
+          <t>04-03-2026 07:19:12</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>04-03-2026 07:18:37</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2333,10 +2337,14 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26120522786620008980</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+          <t>26120522874040009434</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2357,12 +2365,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347769</t>
+          <t>347913</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89934</t>
+          <t>90078</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2372,17 +2380,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VIRGEN ARLETT</t>
+          <t>JESUS ALONSO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PARRA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MORENO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2392,79 +2400,67 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6631079402</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>VALLE REDONDO MZ 3 LT 302</t>
-        </is>
-      </c>
+          <t>6642581633</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>22-01-2004</t>
+          <t>02-01-1991</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ARLETTPARRA8@GMAIL.COM</t>
+          <t>JESUSLONSOASN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 17:49:10</t>
+          <t>02-03-2026 21:34:11</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 17:58:07</t>
+          <t>02-03-2026 21:37:54</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:57:21</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2472,36 +2468,36 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26120522809460009082</t>
+          <t>26120522820940009167</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347597</t>
+          <t>347942</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89762</t>
+          <t>90107</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2511,17 +2507,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BEATRIZ ELENA</t>
+          <t>BETSAIDA GALILEA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>ARIAS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>RAZON</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2531,10 +2527,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6631095288</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>6692339589</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>C FERROCARRIL</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2542,42 +2542,42 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>12-06-1995</t>
+          <t>16-05-2002</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>BAETRIZELENA@GMAIL.COM</t>
+          <t>GALIARIAS10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 14:40:17</t>
+          <t>03-03-2026 06:59:40</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 14:41:19</t>
+          <t>03-03-2026 07:03:01</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2585,13 +2585,21 @@
           <t>02-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>03-03-2026 07:01:46</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2599,19 +2607,19 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26120522795370009022</t>
+          <t>26120522830980009202</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>Kevin Uriel  Aguilar Dionisio</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2623,12 +2631,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347722</t>
+          <t>347769</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89887</t>
+          <t>89934</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2638,17 +2646,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESLY YUCARY</t>
+          <t>VIRGEN ARLETT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ARIZMENDI</t>
+          <t>PARRA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ARCINIEGA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2658,12 +2666,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6647796345</t>
+          <t>6631079402</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>VILLA DEL REAL</t>
+          <t>VALLE REDONDO MZ 3 LT 302</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2673,17 +2681,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22-08-2000</t>
+          <t>22-01-2004</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>NICOLE726.H@GMAIL.COM</t>
+          <t>ARLETTPARRA8@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 17:08:33</t>
+          <t>02-03-2026 17:49:10</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2708,17 +2716,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:57</t>
+          <t>02-03-2026 17:58:07</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-03-2026 17:19:07</t>
+          <t>02-03-2026 17:57:21</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2728,7 +2736,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2738,7 +2746,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26120522805990009068</t>
+          <t>26120522809460009082</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2762,12 +2770,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347785</t>
+          <t>347471</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89950</t>
+          <t>89636</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2777,17 +2785,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PERLA ROSALBA</t>
+          <t>VICTOR HUGO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>URIBE</t>
+          <t>PEREIRA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RUIZ</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2797,47 +2805,43 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6691277001</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>PRIV CAÑADADE LAS ACACIAS 22505 12</t>
-        </is>
-      </c>
+          <t>6642222176</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>27-10-1998</t>
+          <t>05-12-2002</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PERLARUR10@GMAIL.COM</t>
+          <t>VICTORHUGO002@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 18:00:10</t>
+          <t>02-03-2026 09:49:28</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2847,29 +2851,21 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 18:03:30</t>
+          <t>02-03-2026 09:50:47</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>02-03-2026 18:03:04</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -2877,7 +2873,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26120522809950009084</t>
+          <t>26120522786620008980</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2889,7 +2885,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>Kevin Uriel  Aguilar Dionisio</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2901,12 +2897,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347432</t>
+          <t>347614</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89597</t>
+          <t>89779</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2916,17 +2912,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DANNA PAOLA</t>
+          <t>KAREN ISABEL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ROMO</t>
+          <t>RAMIREZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VILLAFAÑA</t>
+          <t>SERRANO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2936,10 +2932,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6631048616</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>6864237953</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -2947,17 +2947,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20-08-2002</t>
+          <t>07-08-1994</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ROMODANNA@GMAIL.COM</t>
+          <t>KARENISABELRAMTEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 08:00:32</t>
+          <t>02-03-2026 15:02:53</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2967,36 +2967,44 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 08:01:52</t>
+          <t>02-03-2026 15:05:09</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>02-03-2026 15:04:45</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3004,36 +3012,36 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26120522783320008941</t>
+          <t>26120522796430009035</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Antonio  Beltran Sanchez</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>348255</t>
+          <t>347597</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90420</t>
+          <t>89762</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3043,17 +3051,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">AYLINE </t>
+          <t>BEATRIZ ELENA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TERCERO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DE LA ROSA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3063,7 +3071,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6658952416</t>
+          <t>6631095288</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3074,17 +3082,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>18-08-2005</t>
+          <t>12-06-1995</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>AYLINETERCEROS@GMAIL.COM</t>
+          <t>BAETRIZELENA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>03-03-2026 19:10:06</t>
+          <t>02-03-2026 14:40:17</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3109,18 +3117,18 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-03-2026 19:11:29</t>
+          <t>02-03-2026 14:41:19</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -3131,7 +3139,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26120522857830009348</t>
+          <t>26120522795370009022</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3143,24 +3151,24 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>348391</t>
+          <t>347722</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90556</t>
+          <t>89887</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3170,17 +3178,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ALEJANDRO</t>
+          <t>ESLY YUCARY</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NESTA</t>
+          <t>ARIZMENDI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PUERTOS</t>
+          <t>ARCINIEGA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3190,32 +3198,32 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6631628130</t>
+          <t>6647796345</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AV PLATA</t>
+          <t>VILLA DEL REAL</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>15-11-1988</t>
+          <t>22-08-2000</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ALEJANDRONESTA60@GMAIL.COM</t>
+          <t>NICOLE726.H@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>04-03-2026 11:17:53</t>
+          <t>02-03-2026 17:08:33</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3240,17 +3248,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>04-03-2026 11:26:01</t>
+          <t>02-03-2026 17:19:57</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>04-03-2026 11:19:46</t>
+          <t>02-03-2026 17:19:07</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3270,7 +3278,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26120522879420009479</t>
+          <t>26120522805990009068</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3282,24 +3290,24 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347652</t>
+          <t>347785</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89817</t>
+          <t>89950</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3309,17 +3317,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MARITZA DHENYS</t>
+          <t>PERLA ROSALBA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>URIBE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LUGO</t>
+          <t>RUIZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3329,10 +3337,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6646939605</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>6691277001</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>PRIV CAÑADADE LAS ACACIAS 22505 12</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3340,56 +3352,64 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>15-10-2003</t>
+          <t>27-10-1998</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>MARITZASNACHEZ@GMAIL.COM</t>
+          <t>PERLARUR10@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-03-2026 15:53:37</t>
+          <t>02-03-2026 18:00:10</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-03-2026 15:55:09</t>
+          <t>02-03-2026 18:03:30</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:03:04</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3397,36 +3417,36 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26120522799140009047</t>
+          <t>26120522809950009084</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347751</t>
+          <t>347652</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89916</t>
+          <t>89817</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3436,17 +3456,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ALEJANDRA</t>
+          <t>MARITZA DHENYS</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SIGUENZA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>LUGO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3456,14 +3476,10 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6643096129</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>PRIV GRANTE 3450 O 46</t>
-        </is>
-      </c>
+          <t>6646939605</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3471,60 +3487,56 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>28-05-1980</t>
+          <t>15-10-2003</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>MMENDOZASIGUENZA@GMAIL.COM</t>
+          <t>MARITZASNACHEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 17:34:49</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>02-03-2026 15:53:37</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (GRUPAL)</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 17:42:50</t>
+          <t>02-03-2026 15:55:09</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>02-03-2026 17:41:55</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3532,36 +3544,36 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26120522807740009074</t>
+          <t>26120522799140009047</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347614</t>
+          <t>348173</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89779</t>
+          <t>90338</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3571,17 +3583,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>KAREN ISABEL</t>
+          <t>ESTEBAN</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAMIREZ</t>
+          <t>ARREOLA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SERRANO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3591,7 +3603,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6864237953</t>
+          <t>6645821899</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3601,47 +3613,47 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>07-08-1994</t>
+          <t>26-06-2003</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>KARENISABELRAMTEZ@GMAIL.COM</t>
+          <t>ESTEBANARREOLASLOEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 15:02:53</t>
+          <t>03-03-2026 17:24:27</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 15:05:09</t>
+          <t>03-03-2026 17:29:05</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3651,7 +3663,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 15:04:45</t>
+          <t>03-03-2026 17:28:40</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3661,7 +3673,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3671,19 +3683,19 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26120522796430009035</t>
+          <t>26120522850960009316</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Juan Antonio  Beltran Sanchez</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3695,12 +3707,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347914</t>
+          <t>347848</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90079</t>
+          <t>90013</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3710,17 +3722,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FRIDA</t>
+          <t>DANIELA ANGELINA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TREJO</t>
+          <t>ARENAS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MARTINEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3730,10 +3742,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6635910806</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>6676627014</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>C DE LOS EUCALIPTOS MZ 32 LT 29 A</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -3741,56 +3757,64 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24-03-1988</t>
+          <t>13-02-2003</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>FRIDAGSMAHS@GMAIL.COM</t>
+          <t>DANNI13ARENAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 21:39:35</t>
+          <t>02-03-2026 18:43:33</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-03-2026 21:40:28</t>
+          <t>02-03-2026 18:51:24</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:50:43</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3798,14 +3822,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26120522820960009168</t>
+          <t>26120522814230009112</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3822,12 +3846,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>348196</t>
+          <t>347879</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90361</t>
+          <t>90044</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3837,17 +3861,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EDGAR ANDRES</t>
+          <t xml:space="preserve">ANDREA </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GOMARA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3857,43 +3881,47 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6642267630</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>6631642692</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30-03-2008</t>
+          <t>18-12-2001</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>GOMARAEDGAR57@GMAIL.COM</t>
+          <t>ANDREASANCHEZSD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>03-03-2026 17:52:01</t>
+          <t>02-03-2026 19:44:09</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3903,21 +3931,29 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>04-03-2026 19:57:53</t>
+          <t>02-03-2026 19:47:39</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:47:08</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -3925,14 +3961,10 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26120522898580009603</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26120522817830009134</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3941,24 +3973,24 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>310500</t>
+          <t>347987</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>90152</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3968,34 +4000,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KAREN VIANEY</t>
+          <t>PEDRO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CUELLAR</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JUAREZ</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6643280099</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>6197611989</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4003,64 +4031,56 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>01-08-2004</t>
+          <t>28-07-1987</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>VIANEYCUELLAR22@GMAIL.COM</t>
+          <t>PEDROALVAREZ8728@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>21-08-2025 05:35:54</t>
+          <t>03-03-2026 09:24:18</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>05-03-2026 18:20:20</t>
+          <t>03-03-2026 09:25:49</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>05-03-2026 18:19:44</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4068,14 +4088,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26120522926720009755</t>
+          <t>26120522834820009220</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4092,12 +4112,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>347879</t>
+          <t>347914</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90044</t>
+          <t>90079</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4107,17 +4127,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANDREA </t>
+          <t>FRIDA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>TREJO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4127,14 +4147,10 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6631642692</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>6635910806</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4142,64 +4158,56 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>18-12-2001</t>
+          <t>24-03-1988</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ANDREASANCHEZSD@GMAIL.COM</t>
+          <t>FRIDAGSMAHS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>02-03-2026 19:44:09</t>
+          <t>02-03-2026 21:39:35</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>02-03-2026 19:47:39</t>
+          <t>02-03-2026 21:40:28</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>02-03-2026 19:47:08</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4207,36 +4215,36 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26120522817830009134</t>
+          <t>26120522820960009168</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347987</t>
+          <t>348093</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90152</t>
+          <t>90258</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4246,87 +4254,99 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PEDRO</t>
+          <t>MONICA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>PEREZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>6642336397</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>12-01-1977</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>MONICAPERESPERES@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:45:08</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:32:06</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:29:34</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>6197611989</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Femenino</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>28-07-1987</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>PEDROALVAREZ8728@GMAIL.COM</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>03-03-2026 09:24:18</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Sin contrato</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>1 MES $899</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>899</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>03-03-2026 09:25:49</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4334,36 +4354,40 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26120522834820009220</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
+          <t>26120522952700009939</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>348073</t>
+          <t>347709</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90238</t>
+          <t>89874</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4373,17 +4397,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KAREN ALEXANDRA</t>
+          <t>BLANCA STEPHANIE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BENITEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>VAZQUEZ</t>
+          <t>ARELLANO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4393,43 +4417,47 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6645821332</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>6658952135</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>03-03-2000</t>
+          <t>31-01-1996</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>HAMKARENSMD@GMAIL.COM</t>
+          <t>BLANXASTEPHAIEES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>03-03-2026 15:01:24</t>
+          <t>02-03-2026 16:51:23</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -4439,21 +4467,29 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>03-03-2026 15:02:44</t>
+          <t>02-03-2026 16:56:27</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:55:58</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4461,7 +4497,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26120522842870009270</t>
+          <t>26120522803950009062</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -4473,24 +4509,24 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>347709</t>
+          <t>347874</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>89874</t>
+          <t>90039</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4500,17 +4536,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BLANCA STEPHANIE</t>
+          <t>PERLA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>URIBE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ARELLANO</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4520,14 +4556,10 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6658952135</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>6643349799</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4535,64 +4567,56 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>31-01-1996</t>
+          <t>12-12-2007</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>BLANXASTEPHAIEES@GMAIL.COM</t>
+          <t>PERLAURIBEPASTEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>02-03-2026 16:51:23</t>
+          <t>02-03-2026 19:40:22</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>02-03-2026 16:56:27</t>
+          <t>02-03-2026 19:42:36</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>02-03-2026 16:55:58</t>
-        </is>
-      </c>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4600,19 +4624,19 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26120522803950009062</t>
+          <t>26120522817540009133</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>Juan Antonio  Beltran Sanchez</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4624,12 +4648,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>347874</t>
+          <t>347751</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90039</t>
+          <t>89916</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4639,17 +4663,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PERLA</t>
+          <t>ALEJANDRA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>URIBE</t>
+          <t>SIGUENZA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4659,10 +4683,14 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6643349799</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>6643096129</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>PRIV GRANTE 3450 O 46</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -4670,56 +4698,60 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12-12-2007</t>
+          <t>28-05-1980</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>PERLAURIBEPASTEL@GMAIL.COM</t>
+          <t>MMENDOZASIGUENZA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-03-2026 19:40:22</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Tarifas 2026 LE</t>
-        </is>
-      </c>
+          <t>02-03-2026 17:34:49</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>DOMICILIADO 12 MESES PLAN FAMILIAR $999 (GRUPAL)</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>999</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-03-2026 19:42:36</t>
+          <t>02-03-2026 17:42:50</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr"/>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:41:55</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -4727,19 +4759,19 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26120522817540009133</t>
+          <t>26120522807740009074</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>999</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Juan Antonio  Beltran Sanchez</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4751,12 +4783,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>347913</t>
+          <t>348073</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90078</t>
+          <t>90238</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4766,17 +4798,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JESUS ALONSO</t>
+          <t>KAREN ALEXANDRA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>BENITEZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4786,7 +4818,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6642581633</t>
+          <t>6645821332</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4797,22 +4829,22 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>02-01-1991</t>
+          <t>03-03-2000</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>JESUSLONSOASN@GMAIL.COM</t>
+          <t>HAMKARENSMD@GMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>02-03-2026 21:34:11</t>
+          <t>03-03-2026 15:01:24</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4822,17 +4854,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>02-03-2026 21:37:54</t>
+          <t>03-03-2026 15:02:44</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -4843,7 +4875,7 @@
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V33" t="inlineStr"/>
@@ -4854,14 +4886,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26120522820940009167</t>
+          <t>26120522842870009270</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -4878,12 +4910,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>347942</t>
+          <t>347405</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>90107</t>
+          <t>89570</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4893,17 +4925,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BETSAIDA GALILEA</t>
+          <t>ITZEL KARINA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ARIAS</t>
+          <t>GAXIOLA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RAZON</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4913,12 +4945,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6692339589</t>
+          <t>6647511082</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>C FERROCARRIL</t>
+          <t>BOCA DELOBO</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4928,22 +4960,22 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>16-05-2002</t>
+          <t>04-01-2005</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>GALIARIAS10@GMAIL.COM</t>
+          <t>KGAXIOLA51@GMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>03-03-2026 06:59:40</t>
+          <t>02-03-2026 06:37:04</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -4953,7 +4985,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -4963,17 +4995,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>03-03-2026 07:03:01</t>
+          <t>02-03-2026 06:39:25</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>03-03-2026 07:01:46</t>
+          <t>02-03-2026 06:38:46</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4993,7 +5025,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26120522830980009202</t>
+          <t>26120522780920008926</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5017,12 +5049,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>347848</t>
+          <t>347441</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90013</t>
+          <t>89606</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5032,17 +5064,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DANIELA ANGELINA</t>
+          <t>RAUL DUARDO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ARENAS</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>OSORNIO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5052,37 +5084,37 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6676627014</t>
+          <t>6648202291</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>C DE LOS EUCALIPTOS MZ 32 LT 29 A</t>
+          <t>C HDA SAN MIGUEL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>13-02-2003</t>
+          <t>15-11-2003</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>DANNI13ARENAS@GMAIL.COM</t>
+          <t>TORRESRAUL383@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>02-03-2026 18:43:33</t>
+          <t>02-03-2026 08:26:25</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -5092,7 +5124,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -5102,17 +5134,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>02-03-2026 18:51:24</t>
+          <t>02-03-2026 08:29:25</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>02-03-2026 18:50:43</t>
+          <t>02-03-2026 08:29:09</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5132,7 +5164,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26120522814230009112</t>
+          <t>26120522784170008951</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5144,24 +5176,24 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Aram Geronimo Garay Alvarado</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>347419</t>
+          <t>347444</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>89584</t>
+          <t>89609</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5171,17 +5203,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS FERNANDO </t>
+          <t>VIVIAN ARLETH</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>VALLES</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SEGURA</t>
+          <t>RENTERIA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5191,37 +5223,37 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6647879129</t>
+          <t>6633288198</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PRIV</t>
+          <t>COL CERRO COL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>22-08-2000</t>
+          <t>07-10-2005</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>LUISFERNANDO11@GMAIL.COM</t>
+          <t>LILIANVALLES171@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>02-03-2026 07:22:04</t>
+          <t>02-03-2026 08:32:44</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -5231,7 +5263,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -5241,17 +5273,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>04-03-2026 07:19:12</t>
+          <t>02-03-2026 08:35:45</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>04-03-2026 07:18:37</t>
+          <t>02-03-2026 08:34:41</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5271,14 +5303,10 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26120522874040009434</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
+          <t>26120522784290008953</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
@@ -5287,7 +5315,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Kevin Uriel  Aguilar Dionisio</t>
+          <t>Aram Geronimo Garay Alvarado</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5299,12 +5327,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>348542</t>
+          <t>348383</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>90707</t>
+          <t>90548</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5314,17 +5342,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JOSEFINA</t>
+          <t>OSWALDO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ARVIZU</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5334,79 +5362,67 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6646659961</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>6645743473</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>19-03-1984</t>
+          <t>19-08-2004</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>JOSEFINASDA@GMAIL.COM</t>
+          <t>OSWALDO.SANCHEZ@UABC.EDU.MX</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>04-03-2026 17:51:53</t>
+          <t>04-03-2026 10:40:25</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>04-03-2026 17:56:02</t>
+          <t>04-03-2026 10:41:47</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>04-03-2026 17:53:44</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5414,36 +5430,36 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26120522892320009556</t>
+          <t>26120522878810009472</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Juan Antonio  Beltran Sanchez</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>348173</t>
+          <t>348256</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>90338</t>
+          <t>90421</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5453,17 +5469,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ESTEBAN</t>
+          <t>JOSSELINE GUADALUPE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ARREOLA</t>
+          <t>TERCERO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>DELA ROSA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5473,79 +5489,67 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6645821899</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
+          <t>6645895152</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>26-06-2003</t>
+          <t>28-10-1998</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>ESTEBANARREOLASLOEZ@GMAIL.COM</t>
+          <t>JOSSELINETERCEROS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>03-03-2026 17:24:27</t>
+          <t>03-03-2026 19:12:32</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>1 MES $899</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>03-03-2026 17:29:05</t>
+          <t>03-03-2026 19:13:32</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>03-03-2026 17:28:40</t>
-        </is>
-      </c>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5553,36 +5557,36 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26120522850960009316</t>
+          <t>26120522857990009349</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>899</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Leslie Camacho Murillo</t>
+          <t>N/D</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>con rutina</t>
+          <t>sin rutina</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>348638</t>
+          <t>348393</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>90803</t>
+          <t>90558</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5592,17 +5596,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NOVEYDA YANETH</t>
+          <t xml:space="preserve">KAREN </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MORENO</t>
+          <t>DE JORGE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MONZON</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5612,32 +5616,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6647451798</t>
+          <t>6642656887</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CTO REAL PEDREGAL</t>
+          <t>PRIV</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>01-12-1987</t>
+          <t>20-10-1991</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>YANETHMORENO8484@GMAIL.COM</t>
+          <t>KARENDEJORGE093@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>05-03-2026 09:03:06</t>
+          <t>04-03-2026 11:28:01</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5662,17 +5666,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>05-03-2026 09:06:16</t>
+          <t>04-03-2026 11:30:00</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>05-03-2026 09:05:19</t>
+          <t>04-03-2026 11:29:08</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5692,7 +5696,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26120522911300009657</t>
+          <t>26120522879500009480</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5716,12 +5720,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>348256</t>
+          <t>348542</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>90421</t>
+          <t>90707</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5731,17 +5735,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>JOSSELINE GUADALUPE</t>
+          <t>JOSEFINA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TERCERO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DELA ROSA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5751,10 +5755,14 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6645895152</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>6646659961</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>Femenino</t>
@@ -5762,17 +5770,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>28-10-1998</t>
+          <t>19-03-1984</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>JOSSELINETERCEROS@GMAIL.COM</t>
+          <t>JOSEFINASDA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-03-2026 19:12:32</t>
+          <t>04-03-2026 17:51:53</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5782,22 +5790,22 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1 MES $899</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-03-2026 19:13:32</t>
+          <t>04-03-2026 17:56:02</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5805,13 +5813,21 @@
           <t>03-04-2026 23:59:59</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>04-03-2026 17:53:44</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5819,36 +5835,36 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26120522857990009349</t>
+          <t>26120522892320009556</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Juan Antonio  Beltran Sanchez</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>348393</t>
+          <t>348196</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90558</t>
+          <t>90361</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5858,17 +5874,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">KAREN </t>
+          <t>EDGAR ANDRES</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DE JORGE</t>
+          <t>GOMARA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5878,14 +5894,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6642656887</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>PRIV</t>
-        </is>
-      </c>
+          <t>6642267630</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Masculino</t>
@@ -5893,32 +5905,32 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>20-10-1991</t>
+          <t>30-03-2008</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>KARENDEJORGE093@GMAIL.COM</t>
+          <t>GOMARAEDGAR57@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>04-03-2026 11:28:01</t>
+          <t>03-03-2026 17:52:01</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Convenio 99</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>Sin contrato</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>CONVENIOS $549</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -5928,29 +5940,21 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>04-03-2026 11:30:00</t>
+          <t>04-03-2026 19:57:53</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>04-03-2026 11:29:08</t>
-        </is>
-      </c>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
           <t>1</t>
         </is>
       </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -5958,10 +5962,14 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26120522879500009480</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
+          <t>26120522898580009603</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
@@ -6072,7 +6080,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -6109,24 +6117,24 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>Leslie Camacho Murillo</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>sin rutina</t>
+          <t>con rutina</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>348383</t>
+          <t>348944</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>90548</t>
+          <t>91109</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6136,17 +6144,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>OSWALDO</t>
+          <t>MARIA GUADALUPE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>GALLARDO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ARVIZU</t>
+          <t>ALAPIZCO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6156,43 +6164,47 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6645743473</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>6664582133</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>19-08-2004</t>
+          <t>29-09-1998</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>OSWALDO.SANCHEZ@UABC.EDU.MX</t>
+          <t>GALLARDOALAPIZCS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>04-03-2026 10:40:25</t>
+          <t>06-03-2026 15:45:17</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Convenio 99</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Sin contrato</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CONVENIOS $549</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -6202,21 +6214,29 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>04-03-2026 10:41:47</t>
+          <t>06-03-2026 15:49:35</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
-        </is>
-      </c>
-      <c r="T43" t="inlineStr"/>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:48:57</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr">
         <is>
           <t>Sucursal</t>
@@ -6224,7 +6244,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26120522878810009472</t>
+          <t>26120522953100009941</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6240,6 +6260,828 @@
         </is>
       </c>
       <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>348638</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>90803</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NOVEYDA YANETH</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>MORENO</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>MONZON</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6647451798</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>CTO REAL PEDREGAL</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>01-12-1987</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>YANETHMORENO8484@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>05-03-2026 09:03:06</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>05-03-2026 09:06:16</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>05-03-2026 09:05:19</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26120522911300009657</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>348846</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>91011</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SILVANO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6648084402</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>HDA SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>09-02-1964</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>SILVANOTORREZJIMENEZ@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:01:07</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:07:00</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:06:09</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26120522944110009858</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Leslie Camacho Murillo</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>con rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>348947</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>91112</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALMA </t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ALAPIZCO</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>OLIVAS</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6645895842</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>02-04-1969</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>ALMADELIA@SSGMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:51:18</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>06-03-2026 16:01:40</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>06-03-2026 15:55:25</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26120522953370009946</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>347963</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>90128</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DULCE YANET</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>GARAY</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>OSUNA</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>6644919254</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>C ANTURIO 9513</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>06-09-1983</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>DULCEGARAY327@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:17:05</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:23:39</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:22:58</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26120522833250009214</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>348255</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>90420</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AYLINE </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TERCERO</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DE LA ROSA</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>6658952416</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>18-08-2005</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>AYLINETERCEROS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:10:06</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Sin contrato</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>1 MES $899</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:11:29</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26120522857830009348</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>348391</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>90556</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>PASEO 2000</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ALEJANDRO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>NESTA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>PUERTOS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>6631628130</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>AV PLATA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>15-11-1988</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>ALEJANDRONESTA60@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>04-03-2026 11:17:53</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>04-03-2026 11:26:01</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>04-03-2026 11:19:46</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26120522879420009479</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
